--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-tiflow-operation-outcome.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-tiflow-operation-outcome.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="209">
   <si>
     <t>Property</t>
   </si>
@@ -439,6 +439,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -473,6 +483,10 @@
   </si>
   <si>
     <t>An error, warning, or information message that results from a system action.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>AcknowledgementDetail or Observation[classCode="ALRT" and moodCode="EVN"]</t>
@@ -1004,7 +1018,7 @@
     <col min="26" max="26" width="59.46484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1960,19 +1974,19 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -1984,7 +1998,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>129</v>
@@ -1995,10 +2009,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2024,16 +2038,16 @@
         <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>135</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2070,19 +2084,19 @@
         <v>76</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2094,7 +2108,7 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>129</v>
@@ -2105,10 +2119,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2131,13 +2145,13 @@
         <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2188,7 +2202,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>86</v>
@@ -2197,24 +2211,24 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2237,13 +2251,13 @@
         <v>76</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2294,7 +2308,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2309,7 +2323,7 @@
         <v>76</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>76</v>
@@ -2317,10 +2331,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2349,7 +2363,7 @@
         <v>133</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s" s="2">
         <v>135</v>
@@ -2390,19 +2404,19 @@
         <v>76</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2414,10 +2428,10 @@
         <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
@@ -2425,14 +2439,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2454,16 +2468,16 @@
         <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>135</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>76</v>
@@ -2512,7 +2526,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2524,7 +2538,7 @@
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>129</v>
@@ -2535,10 +2549,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2564,16 +2578,16 @@
         <v>106</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -2598,13 +2612,13 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>76</v>
@@ -2622,7 +2636,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>86</v>
@@ -2637,18 +2651,18 @@
         <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2674,14 +2688,14 @@
         <v>106</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -2706,31 +2720,31 @@
         <v>76</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>86</v>
@@ -2745,18 +2759,18 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2779,16 +2793,16 @@
         <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2814,11 +2828,11 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>76</v>
@@ -2836,7 +2850,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -2845,24 +2859,24 @@
         <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2885,16 +2899,16 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2944,7 +2958,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -2959,18 +2973,18 @@
         <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2993,19 +3007,19 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3054,7 +3068,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3069,18 +3083,18 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3103,19 +3117,19 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3164,7 +3178,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3179,10 +3193,10 @@
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
